--- a/tests/Test_Report.xlsx
+++ b/tests/Test_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="148">
   <si>
     <t>Module</t>
   </si>
@@ -58,61 +58,88 @@
     <t>Đăng ký thất bại với email đã tồn tại</t>
   </si>
   <si>
+    <t>TC_REG_04</t>
+  </si>
+  <si>
+    <t>Đăng ký thất bại khi nhập email sai định dạng</t>
+  </si>
+  <si>
+    <t>TC_REG_05</t>
+  </si>
+  <si>
+    <t>Đăng ký thất bại khi mật khẩu quá ngắn</t>
+  </si>
+  <si>
+    <t>TC_REG_06</t>
+  </si>
+  <si>
+    <t>Đăng ký thất bại khi để trống tên người dùng</t>
+  </si>
+  <si>
+    <t>TC_REG_07</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công với email có khoảng trắng ở đầu/cuối</t>
+  </si>
+  <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>expected '' to satisfy [Function]</t>
-  </si>
-  <si>
-    <t>TC_REG_04</t>
-  </si>
-  <si>
-    <t>Đăng ký thất bại khi nhập email sai định dạng</t>
-  </si>
-  <si>
-    <t>TC_REG_05</t>
-  </si>
-  <si>
-    <t>Đăng ký thất bại khi mật khẩu quá ngắn</t>
+    <t>expected '' to include 'thành công'</t>
+  </si>
+  <si>
+    <t>TC_REG_08</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút "Đăng nhập" dẫn về trang login.html</t>
+  </si>
+  <si>
+    <t>TC_REG_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo thành công hiển thị đúng nội dung</t>
+  </si>
+  <si>
+    <t>expected '' to include 'đăng ký thành công'</t>
+  </si>
+  <si>
+    <t>TC_REG_10</t>
+  </si>
+  <si>
+    <t>Tự động chuyển hướng sang trang Login sau khi đăng ký</t>
+  </si>
+  <si>
+    <t>TC_REG_11</t>
+  </si>
+  <si>
+    <t>Đăng ký với tên người dùng rất dài</t>
   </si>
   <si>
     <t>expected false to be true</t>
   </si>
   <si>
-    <t>TC_REG_06</t>
-  </si>
-  <si>
-    <t>Đăng ký thất bại khi để trống tên người dùng</t>
-  </si>
-  <si>
-    <t>TC_REG_07</t>
-  </si>
-  <si>
-    <t>Đăng ký thành công với email có khoảng trắng ở đầu/cuối</t>
-  </si>
-  <si>
-    <t>expected '' to include 'thành công'</t>
-  </si>
-  <si>
-    <t>TC_REG_08</t>
-  </si>
-  <si>
-    <t>Kiểm tra nút "Đăng nhập" dẫn về trang login.html</t>
-  </si>
-  <si>
-    <t>TC_REG_09</t>
-  </si>
-  <si>
-    <t>Kiểm tra thông báo thành công hiển thị đúng nội dung</t>
-  </si>
-  <si>
-    <t>expected '' to include 'đăng ký thành công'</t>
-  </si>
-  <si>
-    <t>TC_REG_10</t>
-  </si>
-  <si>
-    <t>Tự động chuyển hướng sang trang Login sau khi đăng ký</t>
+    <t>TC_REG_12</t>
+  </si>
+  <si>
+    <t>Đăng ký với email chứa ký tự đặc biệt hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_REG_13</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút Đăng ký có bị vô hiệu hóa sau khi click</t>
+  </si>
+  <si>
+    <t>TC_REG_14</t>
+  </si>
+  <si>
+    <t>Kiểm tra quay lại trang chủ qua link Đăng nhập rồi về Home</t>
+  </si>
+  <si>
+    <t>TC_REG_15</t>
+  </si>
+  <si>
+    <t>Đăng ký với mật khẩu chứa toàn khoảng trắng</t>
   </si>
   <si>
     <t>Login</t>
@@ -124,69 +151,317 @@
     <t>Đăng nhập thành công với tài khoản User</t>
   </si>
   <si>
+    <t>TC_LOG_02</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công với tài khoản Admin</t>
+  </si>
+  <si>
+    <t>TC_LOG_03</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại khi sai mật khẩu</t>
+  </si>
+  <si>
+    <t>TC_LOG_04</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại với email không tồn tại</t>
+  </si>
+  <si>
+    <t>expected '' to include 'không tồn tại'</t>
+  </si>
+  <si>
+    <t>TC_LOG_05</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại khi để trống email</t>
+  </si>
+  <si>
+    <t>TC_LOG_06</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại khi để trống mật khẩu</t>
+  </si>
+  <si>
+    <t>TC_LOG_07</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại khi email sai định dạng</t>
+  </si>
+  <si>
+    <t>TC_LOG_08</t>
+  </si>
+  <si>
+    <t>Kiểm tra Token được lưu vào LocalStorage sau khi đăng nhập</t>
+  </si>
+  <si>
+    <t>TC_LOG_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút "Đăng ký" dẫn về trang register.html</t>
+  </si>
+  <si>
+    <t>TC_LOG_10</t>
+  </si>
+  <si>
+    <t>Kiểm tra trạng thái đăng nhập được duy trì sau khi tải lại trang (F5)</t>
+  </si>
+  <si>
+    <t>TC_LOG_11</t>
+  </si>
+  <si>
+    <t>Đăng xuất thành công</t>
+  </si>
+  <si>
+    <t>TC_LOG_12</t>
+  </si>
+  <si>
+    <t>Đăng nhập với Email viết hoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waiting for URL to contain "index.html"
-Wait timed out after 20077ms</t>
-  </si>
-  <si>
-    <t>TC_LOG_02</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công với tài khoản Admin</t>
-  </si>
-  <si>
-    <t>TC_LOG_03</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại khi sai mật khẩu</t>
-  </si>
-  <si>
-    <t>TC_LOG_04</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại với email không tồn tại</t>
-  </si>
-  <si>
-    <t>expected '' to include 'không tồn tại'</t>
-  </si>
-  <si>
-    <t>TC_LOG_05</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại khi để trống email</t>
-  </si>
-  <si>
-    <t>TC_LOG_06</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại khi để trống mật khẩu</t>
-  </si>
-  <si>
-    <t>TC_LOG_07</t>
-  </si>
-  <si>
-    <t>Đăng nhập thất bại khi email sai định dạng</t>
-  </si>
-  <si>
-    <t>TC_LOG_08</t>
-  </si>
-  <si>
-    <t>Kiểm tra Token được lưu vào LocalStorage sau khi đăng nhập</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for URL to contain "index.html"
-Wait timed out after 10213ms</t>
-  </si>
-  <si>
-    <t>TC_LOG_09</t>
-  </si>
-  <si>
-    <t>Kiểm tra nút "Đăng ký" dẫn về trang register.html</t>
-  </si>
-  <si>
-    <t>TC_LOG_10</t>
-  </si>
-  <si>
-    <t>Kiểm tra trạng thái đăng nhập được duy trì sau khi tải lại trang (F5)</t>
+Wait timed out after 10011ms</t>
+  </si>
+  <si>
+    <t>TC_LOG_13</t>
+  </si>
+  <si>
+    <t>Truy cập trang Login khi đã đăng nhập</t>
+  </si>
+  <si>
+    <t>TC_LOG_14</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị tên người dùng trên Header</t>
+  </si>
+  <si>
+    <t>expected 'Đăng nhập\nĐăng ký' to include 'Chào'</t>
+  </si>
+  <si>
+    <t>TC_LOG_15</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông tin liên hệ ở chân trang Login</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>TC_CRT_01</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm thành công từ trang chủ</t>
+  </si>
+  <si>
+    <t>TC_CRT_02</t>
+  </si>
+  <si>
+    <t>Kiểm tra Badge giỏ hàng tăng lên khi thêm sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_CRT_03</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm từ trang chi tiết sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_CRT_04</t>
+  </si>
+  <si>
+    <t>Thêm nhiều sản phẩm khác nhau vào giỏ hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aborted by navigation: Not attached to an active page
+  (Session info: chrome=146.0.7680.165)</t>
+  </si>
+  <si>
+    <t>TC_CRT_05</t>
+  </si>
+  <si>
+    <t>Thêm cùng một sản phẩm nhiều lần</t>
+  </si>
+  <si>
+    <t>TC_CRT_06</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>TC_CRT_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra sản phẩm trong giỏ hàng khớp với sản phẩm đã chọn</t>
+  </si>
+  <si>
+    <t>TC_CRT_08</t>
+  </si>
+  <si>
+    <t>Badge giỏ hàng cập nhật ngay lập tức</t>
+  </si>
+  <si>
+    <t>TC_CRT_09</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm sau khi tìm kiếm</t>
+  </si>
+  <si>
+    <t>TC_CRT_10</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm sau khi lọc theo danh mục</t>
+  </si>
+  <si>
+    <t>TC_CRT_11</t>
+  </si>
+  <si>
+    <t>Quay lại trang chi tiết sản phẩm từ giỏ hàng</t>
+  </si>
+  <si>
+    <t>TC_CRT_12</t>
+  </si>
+  <si>
+    <t>Kiểm tra giỏ hàng sau khi logout/login lại</t>
+  </si>
+  <si>
+    <t>TC_CRT_13</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm có giá trị lớn</t>
+  </si>
+  <si>
+    <t>TC_CRT_14</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm và kiểm tra Subtotal</t>
+  </si>
+  <si>
+    <t>TC_CRT_15</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo khi thêm thành công</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>TC_ORD_01</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công với đầy đủ thông tin (COD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unexpected alert open: {Alert text : Lỗi: Sản phẩm Beagle Puppy không đủ số lượng trong kho!}
+  (Session info: chrome=146.0.7680.165)</t>
+  </si>
+  <si>
+    <t>TC_ORD_02</t>
+  </si>
+  <si>
+    <t>Đặt hàng thất bại khi thiếu Số điện thoại</t>
+  </si>
+  <si>
+    <t>TC_ORD_03</t>
+  </si>
+  <si>
+    <t>Đặt hàng thất bại khi thiếu Địa chỉ giao hàng</t>
+  </si>
+  <si>
+    <t>TC_ORD_04</t>
+  </si>
+  <si>
+    <t>Đặt hàng thất bại khi thiếu Họ tên người nhận</t>
+  </si>
+  <si>
+    <t>TC_ORD_05</t>
+  </si>
+  <si>
+    <t>Kiểm tra tổng tiền đơn hàng khớp với giỏ hàng</t>
+  </si>
+  <si>
+    <t>expected '34.038 ₫' to include 'đ'</t>
+  </si>
+  <si>
+    <t>TC_ORD_06</t>
+  </si>
+  <si>
+    <t>Tự động chuyển hướng về "Lịch sử đơn hàng"</t>
+  </si>
+  <si>
+    <t>TC_ORD_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra đơn hàng mới xuất hiện trong danh sách lịch sử</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for at least one element to be located By(css selector, .order-card)
+Wait timed out after 10130ms</t>
+  </si>
+  <si>
+    <t>TC_ORD_08</t>
+  </si>
+  <si>
+    <t>Trạng thái đơn hàng mới mặc định là "Pending"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, .order-card)
+Wait timed out after 10151ms</t>
+  </si>
+  <si>
+    <t>TC_ORD_09</t>
+  </si>
+  <si>
+    <t>Xem chi tiết đơn hàng vừa đặt qua Modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":".order-card"}
+  (Session info: chrome=146.0.7680.165)</t>
+  </si>
+  <si>
+    <t>TC_ORD_10</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công với đơn hàng có nhiều sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_ORD_11</t>
+  </si>
+  <si>
+    <t>Đặt hàng với số điện thoại sai định dạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":".btn-add-cart"}
+  (Session info: chrome=146.0.7680.165)</t>
+  </si>
+  <si>
+    <t>TC_ORD_12</t>
+  </si>
+  <si>
+    <t>Kiểm tra giỏ hàng bị xóa sạch sau khi đặt hàng</t>
+  </si>
+  <si>
+    <t>expected '44' to equal '0'</t>
+  </si>
+  <si>
+    <t>TC_ORD_13</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông tin địa chỉ lưu đúng trong chi tiết đơn hàng</t>
+  </si>
+  <si>
+    <t>TC_ORD_14</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút quay lại giỏ hàng từ trang Thanh toán</t>
+  </si>
+  <si>
+    <t>TC_ORD_15</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị ngày đặt hàng</t>
+  </si>
+  <si>
+    <t>expected '📅 Ngày đặt: 29/3/2026\n📍 Giao đến: …' to match /\d{2}\/\d{2}\/\d{4}/</t>
   </si>
 </sst>
 </file>
@@ -582,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -630,7 +905,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>717</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -663,14 +938,14 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -678,10 +953,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -690,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -698,19 +973,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -718,10 +993,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -730,7 +1005,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>117</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -738,19 +1013,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
       <c r="F8">
-        <v>147</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -758,10 +1033,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -770,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -778,19 +1053,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
       <c r="F10">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,10 +1073,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -810,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>2305</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -818,19 +1093,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>717</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -838,19 +1113,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -858,19 +1133,19 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>15</v>
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -878,10 +1153,10 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>9</v>
@@ -890,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -898,19 +1173,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -918,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>9</v>
@@ -930,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>117</v>
+        <v>634</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -938,19 +1213,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>147</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -958,10 +1233,10 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>9</v>
@@ -970,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>83</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -978,19 +1253,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>147</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,10 +1273,10 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>9</v>
@@ -1010,98 +1285,98 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>2305</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>20477</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>325</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>118</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
@@ -1110,78 +1385,78 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>94</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
       <c r="F27">
-        <v>128</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
         <v>34</v>
       </c>
-      <c r="B28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
       <c r="F28">
-        <v>112</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>15</v>
+        <v>38</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>10328</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>9</v>
@@ -1190,18 +1465,18 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>9</v>
@@ -1210,18 +1485,18 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>98</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>9</v>
@@ -1230,18 +1505,18 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>717</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>9</v>
@@ -1250,78 +1525,78 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>70</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F34">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>15</v>
+        <v>54</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>142</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
@@ -1330,38 +1605,38 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>9</v>
@@ -1370,38 +1645,38 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>83</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>15</v>
+        <v>62</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>147</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>9</v>
@@ -1410,98 +1685,98 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>2305</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>15</v>
+        <v>66</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>20477</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="F43">
-        <v>325</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>15</v>
+        <v>71</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>126</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F45">
-        <v>118</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>9</v>
@@ -1510,18 +1785,18 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
@@ -1530,18 +1805,18 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>128</v>
+        <v>634</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
@@ -1550,38 +1825,38 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F49">
-        <v>10328</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>9</v>
@@ -1590,18 +1865,18 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>9</v>
@@ -1610,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>98</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1618,10 +1893,10 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>9</v>
@@ -1630,7 +1905,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>717</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1638,19 +1913,19 @@
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F53">
-        <v>70</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1658,19 +1933,19 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F54">
-        <v>185</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1678,19 +1953,19 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F55">
-        <v>80</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1698,19 +1973,19 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>142</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,19 +1993,19 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F57">
-        <v>117</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1738,19 +2013,19 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F58">
-        <v>147</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,10 +2033,10 @@
         <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>9</v>
@@ -1770,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>83</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1778,19 +2053,19 @@
         <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F60">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1798,10 +2073,10 @@
         <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
@@ -1810,38 +2085,38 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>2305</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>20477</v>
+        <v>729</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>9</v>
@@ -1850,58 +2125,58 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
         <v>34</v>
       </c>
-      <c r="B64" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" t="s">
-        <v>41</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" t="s">
-        <v>21</v>
-      </c>
       <c r="F64">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B65" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F65">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
@@ -1910,18 +2185,18 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>9</v>
@@ -1930,18 +2205,18 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -1950,38 +2225,38 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>112</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>10328</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>9</v>
@@ -1990,18 +2265,18 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
@@ -2010,18 +2285,18 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>9</v>
@@ -2030,98 +2305,98 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>717</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="F73">
-        <v>70</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>15</v>
+        <v>71</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F74">
-        <v>185</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>73</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F75">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>20</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>15</v>
+        <v>76</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F76">
-        <v>142</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
@@ -2130,38 +2405,38 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>117</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>15</v>
+        <v>81</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F78">
-        <v>147</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>9</v>
@@ -2170,247 +2445,2647 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>83</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="F80">
-        <v>147</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>88</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F81">
-        <v>2305</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F82">
-        <v>20477</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>92</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F83">
-        <v>325</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="F84">
-        <v>126</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="F85">
-        <v>118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C86" t="s">
-        <v>46</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>98</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F86">
-        <v>94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>48</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F87">
-        <v>128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>102</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F88">
-        <v>112</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C89" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F89">
-        <v>10328</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C90" t="s">
-        <v>55</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>106</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F90">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>77</v>
+      </c>
+      <c r="B91" t="s">
+        <v>107</v>
+      </c>
+      <c r="C91" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" t="s">
+        <v>86</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" t="s">
         <v>34</v>
       </c>
-      <c r="B91" t="s">
+      <c r="F102">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" t="s">
+        <v>34</v>
+      </c>
+      <c r="F103">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" t="s">
+        <v>38</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106" t="s">
+        <v>42</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>43</v>
+      </c>
+      <c r="B107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>43</v>
+      </c>
+      <c r="B108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" t="s">
+        <v>47</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>43</v>
+      </c>
+      <c r="B109" t="s">
+        <v>48</v>
+      </c>
+      <c r="C109" t="s">
+        <v>49</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" t="s">
+        <v>34</v>
+      </c>
+      <c r="F109">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110" t="s">
+        <v>51</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="s">
+        <v>53</v>
+      </c>
+      <c r="C111" t="s">
+        <v>54</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" t="s">
         <v>56</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>43</v>
+      </c>
+      <c r="B113" t="s">
         <v>57</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91">
+      <c r="C113" t="s">
+        <v>58</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s">
+        <v>59</v>
+      </c>
+      <c r="C114" t="s">
+        <v>60</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>43</v>
+      </c>
+      <c r="B115" t="s">
+        <v>61</v>
+      </c>
+      <c r="C115" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>43</v>
+      </c>
+      <c r="B116" t="s">
+        <v>63</v>
+      </c>
+      <c r="C116" t="s">
+        <v>64</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>43</v>
+      </c>
+      <c r="B117" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" t="s">
+        <v>66</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>43</v>
+      </c>
+      <c r="B118" t="s">
+        <v>67</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" t="s">
+        <v>69</v>
+      </c>
+      <c r="F118">
+        <v>10147</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" t="s">
+        <v>70</v>
+      </c>
+      <c r="C119" t="s">
+        <v>71</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>43</v>
+      </c>
+      <c r="B120" t="s">
+        <v>72</v>
+      </c>
+      <c r="C120" t="s">
+        <v>73</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" t="s">
+        <v>74</v>
+      </c>
+      <c r="F120">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>43</v>
+      </c>
+      <c r="B121" t="s">
+        <v>75</v>
+      </c>
+      <c r="C121" t="s">
+        <v>76</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>77</v>
+      </c>
+      <c r="B122" t="s">
+        <v>78</v>
+      </c>
+      <c r="C122" t="s">
+        <v>79</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>77</v>
+      </c>
+      <c r="B123" t="s">
+        <v>80</v>
+      </c>
+      <c r="C123" t="s">
+        <v>81</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>77</v>
+      </c>
+      <c r="B124" t="s">
+        <v>82</v>
+      </c>
+      <c r="C124" t="s">
+        <v>83</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>77</v>
+      </c>
+      <c r="B125" t="s">
+        <v>84</v>
+      </c>
+      <c r="C125" t="s">
+        <v>85</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" t="s">
+        <v>86</v>
+      </c>
+      <c r="F125">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>77</v>
+      </c>
+      <c r="B126" t="s">
+        <v>87</v>
+      </c>
+      <c r="C126" t="s">
+        <v>88</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" t="s">
+        <v>86</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>77</v>
+      </c>
+      <c r="B127" t="s">
+        <v>89</v>
+      </c>
+      <c r="C127" t="s">
+        <v>90</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" t="s">
+        <v>86</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>77</v>
+      </c>
+      <c r="B128" t="s">
+        <v>91</v>
+      </c>
+      <c r="C128" t="s">
+        <v>92</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" t="s">
+        <v>86</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>77</v>
+      </c>
+      <c r="B129" t="s">
+        <v>93</v>
+      </c>
+      <c r="C129" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" t="s">
+        <v>86</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>77</v>
+      </c>
+      <c r="B130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" t="s">
+        <v>86</v>
+      </c>
+      <c r="F130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>77</v>
+      </c>
+      <c r="B131" t="s">
+        <v>97</v>
+      </c>
+      <c r="C131" t="s">
         <v>98</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131" t="s">
+        <v>86</v>
+      </c>
+      <c r="F131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>77</v>
+      </c>
+      <c r="B132" t="s">
+        <v>99</v>
+      </c>
+      <c r="C132" t="s">
+        <v>100</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" t="s">
+        <v>86</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>77</v>
+      </c>
+      <c r="B133" t="s">
+        <v>101</v>
+      </c>
+      <c r="C133" t="s">
+        <v>102</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" t="s">
+        <v>86</v>
+      </c>
+      <c r="F133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>77</v>
+      </c>
+      <c r="B134" t="s">
+        <v>103</v>
+      </c>
+      <c r="C134" t="s">
+        <v>104</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134" t="s">
+        <v>86</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>77</v>
+      </c>
+      <c r="B135" t="s">
+        <v>105</v>
+      </c>
+      <c r="C135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E135" t="s">
+        <v>86</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>77</v>
+      </c>
+      <c r="B136" t="s">
+        <v>107</v>
+      </c>
+      <c r="C136" t="s">
+        <v>108</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" t="s">
+        <v>86</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>109</v>
+      </c>
+      <c r="B137" t="s">
+        <v>110</v>
+      </c>
+      <c r="C137" t="s">
+        <v>111</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" t="s">
+        <v>112</v>
+      </c>
+      <c r="F137">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>109</v>
+      </c>
+      <c r="B138" t="s">
+        <v>113</v>
+      </c>
+      <c r="C138" t="s">
+        <v>114</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>109</v>
+      </c>
+      <c r="B139" t="s">
+        <v>115</v>
+      </c>
+      <c r="C139" t="s">
+        <v>116</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>109</v>
+      </c>
+      <c r="B140" t="s">
+        <v>117</v>
+      </c>
+      <c r="C140" t="s">
+        <v>118</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>109</v>
+      </c>
+      <c r="B141" t="s">
+        <v>119</v>
+      </c>
+      <c r="C141" t="s">
+        <v>120</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" t="s">
+        <v>121</v>
+      </c>
+      <c r="F141">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>109</v>
+      </c>
+      <c r="B142" t="s">
+        <v>122</v>
+      </c>
+      <c r="C142" t="s">
+        <v>123</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" t="s">
+        <v>112</v>
+      </c>
+      <c r="F142">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>109</v>
+      </c>
+      <c r="B143" t="s">
+        <v>124</v>
+      </c>
+      <c r="C143" t="s">
+        <v>125</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" t="s">
+        <v>126</v>
+      </c>
+      <c r="F143">
+        <v>10130</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>109</v>
+      </c>
+      <c r="B144" t="s">
+        <v>127</v>
+      </c>
+      <c r="C144" t="s">
+        <v>128</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144">
+        <v>10151</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>109</v>
+      </c>
+      <c r="B145" t="s">
+        <v>130</v>
+      </c>
+      <c r="C145" t="s">
+        <v>131</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" t="s">
+        <v>132</v>
+      </c>
+      <c r="F145">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>109</v>
+      </c>
+      <c r="B146" t="s">
+        <v>133</v>
+      </c>
+      <c r="C146" t="s">
+        <v>134</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" t="s">
+        <v>112</v>
+      </c>
+      <c r="F146">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>109</v>
+      </c>
+      <c r="B147" t="s">
+        <v>135</v>
+      </c>
+      <c r="C147" t="s">
+        <v>136</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" t="s">
+        <v>137</v>
+      </c>
+      <c r="F147">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>109</v>
+      </c>
+      <c r="B148" t="s">
+        <v>138</v>
+      </c>
+      <c r="C148" t="s">
+        <v>139</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" t="s">
+        <v>140</v>
+      </c>
+      <c r="F148">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>109</v>
+      </c>
+      <c r="B149" t="s">
+        <v>141</v>
+      </c>
+      <c r="C149" t="s">
+        <v>142</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" t="s">
+        <v>34</v>
+      </c>
+      <c r="F149">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>109</v>
+      </c>
+      <c r="B150" t="s">
+        <v>143</v>
+      </c>
+      <c r="C150" t="s">
+        <v>144</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>109</v>
+      </c>
+      <c r="B151" t="s">
+        <v>145</v>
+      </c>
+      <c r="C151" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" t="s">
+        <v>147</v>
+      </c>
+      <c r="F151">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>6</v>
+      </c>
+      <c r="B152" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>6</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>6</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" t="s">
+        <v>16</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>6</v>
+      </c>
+      <c r="B156" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>6</v>
+      </c>
+      <c r="B157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>6</v>
+      </c>
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" t="s">
+        <v>22</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>6</v>
+      </c>
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" t="s">
+        <v>26</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>6</v>
+      </c>
+      <c r="B160" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160" t="s">
+        <v>28</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" t="s">
+        <v>29</v>
+      </c>
+      <c r="F160">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161" t="s">
+        <v>31</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" t="s">
+        <v>32</v>
+      </c>
+      <c r="C162" t="s">
+        <v>33</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" t="s">
+        <v>34</v>
+      </c>
+      <c r="F162">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" t="s">
+        <v>35</v>
+      </c>
+      <c r="C163" t="s">
+        <v>36</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" t="s">
+        <v>34</v>
+      </c>
+      <c r="F163">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" t="s">
+        <v>37</v>
+      </c>
+      <c r="C164" t="s">
+        <v>38</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" t="s">
+        <v>39</v>
+      </c>
+      <c r="C165" t="s">
+        <v>40</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" t="s">
+        <v>41</v>
+      </c>
+      <c r="C166" t="s">
+        <v>42</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>43</v>
+      </c>
+      <c r="B167" t="s">
+        <v>44</v>
+      </c>
+      <c r="C167" t="s">
+        <v>45</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>43</v>
+      </c>
+      <c r="B168" t="s">
+        <v>46</v>
+      </c>
+      <c r="C168" t="s">
+        <v>47</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>43</v>
+      </c>
+      <c r="B169" t="s">
+        <v>48</v>
+      </c>
+      <c r="C169" t="s">
+        <v>49</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169" t="s">
+        <v>34</v>
+      </c>
+      <c r="F169">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>43</v>
+      </c>
+      <c r="B170" t="s">
+        <v>50</v>
+      </c>
+      <c r="C170" t="s">
+        <v>51</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E170" t="s">
+        <v>52</v>
+      </c>
+      <c r="F170">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>43</v>
+      </c>
+      <c r="B171" t="s">
+        <v>53</v>
+      </c>
+      <c r="C171" t="s">
+        <v>54</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>43</v>
+      </c>
+      <c r="B172" t="s">
+        <v>55</v>
+      </c>
+      <c r="C172" t="s">
+        <v>56</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>43</v>
+      </c>
+      <c r="B173" t="s">
+        <v>57</v>
+      </c>
+      <c r="C173" t="s">
+        <v>58</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>43</v>
+      </c>
+      <c r="B174" t="s">
+        <v>59</v>
+      </c>
+      <c r="C174" t="s">
+        <v>60</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>10</v>
+      </c>
+      <c r="F174">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>43</v>
+      </c>
+      <c r="B175" t="s">
+        <v>61</v>
+      </c>
+      <c r="C175" t="s">
+        <v>62</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>43</v>
+      </c>
+      <c r="B176" t="s">
+        <v>63</v>
+      </c>
+      <c r="C176" t="s">
+        <v>64</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>43</v>
+      </c>
+      <c r="B177" t="s">
+        <v>65</v>
+      </c>
+      <c r="C177" t="s">
+        <v>66</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>43</v>
+      </c>
+      <c r="B178" t="s">
+        <v>67</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E178" t="s">
+        <v>69</v>
+      </c>
+      <c r="F178">
+        <v>10147</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>43</v>
+      </c>
+      <c r="B179" t="s">
+        <v>70</v>
+      </c>
+      <c r="C179" t="s">
+        <v>71</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>43</v>
+      </c>
+      <c r="B180" t="s">
+        <v>72</v>
+      </c>
+      <c r="C180" t="s">
+        <v>73</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E180" t="s">
+        <v>74</v>
+      </c>
+      <c r="F180">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>43</v>
+      </c>
+      <c r="B181" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" t="s">
+        <v>76</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" t="s">
+        <v>10</v>
+      </c>
+      <c r="F181">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>77</v>
+      </c>
+      <c r="B182" t="s">
+        <v>78</v>
+      </c>
+      <c r="C182" t="s">
+        <v>79</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>77</v>
+      </c>
+      <c r="B183" t="s">
+        <v>80</v>
+      </c>
+      <c r="C183" t="s">
+        <v>81</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>77</v>
+      </c>
+      <c r="B184" t="s">
+        <v>82</v>
+      </c>
+      <c r="C184" t="s">
+        <v>83</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>77</v>
+      </c>
+      <c r="B185" t="s">
+        <v>84</v>
+      </c>
+      <c r="C185" t="s">
+        <v>85</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" t="s">
+        <v>86</v>
+      </c>
+      <c r="F185">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>77</v>
+      </c>
+      <c r="B186" t="s">
+        <v>87</v>
+      </c>
+      <c r="C186" t="s">
+        <v>88</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E186" t="s">
+        <v>86</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>77</v>
+      </c>
+      <c r="B187" t="s">
+        <v>89</v>
+      </c>
+      <c r="C187" t="s">
+        <v>90</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E187" t="s">
+        <v>86</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>77</v>
+      </c>
+      <c r="B188" t="s">
+        <v>91</v>
+      </c>
+      <c r="C188" t="s">
+        <v>92</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" t="s">
+        <v>86</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>77</v>
+      </c>
+      <c r="B189" t="s">
+        <v>93</v>
+      </c>
+      <c r="C189" t="s">
+        <v>94</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E189" t="s">
+        <v>86</v>
+      </c>
+      <c r="F189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>77</v>
+      </c>
+      <c r="B190" t="s">
+        <v>95</v>
+      </c>
+      <c r="C190" t="s">
+        <v>96</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E190" t="s">
+        <v>86</v>
+      </c>
+      <c r="F190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>77</v>
+      </c>
+      <c r="B191" t="s">
+        <v>97</v>
+      </c>
+      <c r="C191" t="s">
+        <v>98</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E191" t="s">
+        <v>86</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>77</v>
+      </c>
+      <c r="B192" t="s">
+        <v>99</v>
+      </c>
+      <c r="C192" t="s">
+        <v>100</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E192" t="s">
+        <v>86</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>77</v>
+      </c>
+      <c r="B193" t="s">
+        <v>101</v>
+      </c>
+      <c r="C193" t="s">
+        <v>102</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E193" t="s">
+        <v>86</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>77</v>
+      </c>
+      <c r="B194" t="s">
+        <v>103</v>
+      </c>
+      <c r="C194" t="s">
+        <v>104</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E194" t="s">
+        <v>86</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>77</v>
+      </c>
+      <c r="B195" t="s">
+        <v>105</v>
+      </c>
+      <c r="C195" t="s">
+        <v>106</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E195" t="s">
+        <v>86</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>77</v>
+      </c>
+      <c r="B196" t="s">
+        <v>107</v>
+      </c>
+      <c r="C196" t="s">
+        <v>108</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" t="s">
+        <v>86</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>109</v>
+      </c>
+      <c r="B197" t="s">
+        <v>110</v>
+      </c>
+      <c r="C197" t="s">
+        <v>111</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E197" t="s">
+        <v>112</v>
+      </c>
+      <c r="F197">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>109</v>
+      </c>
+      <c r="B198" t="s">
+        <v>113</v>
+      </c>
+      <c r="C198" t="s">
+        <v>114</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>109</v>
+      </c>
+      <c r="B199" t="s">
+        <v>115</v>
+      </c>
+      <c r="C199" t="s">
+        <v>116</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>109</v>
+      </c>
+      <c r="B200" t="s">
+        <v>117</v>
+      </c>
+      <c r="C200" t="s">
+        <v>118</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>109</v>
+      </c>
+      <c r="B201" t="s">
+        <v>119</v>
+      </c>
+      <c r="C201" t="s">
+        <v>120</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E201" t="s">
+        <v>121</v>
+      </c>
+      <c r="F201">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>109</v>
+      </c>
+      <c r="B202" t="s">
+        <v>122</v>
+      </c>
+      <c r="C202" t="s">
+        <v>123</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E202" t="s">
+        <v>112</v>
+      </c>
+      <c r="F202">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>109</v>
+      </c>
+      <c r="B203" t="s">
+        <v>124</v>
+      </c>
+      <c r="C203" t="s">
+        <v>125</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E203" t="s">
+        <v>126</v>
+      </c>
+      <c r="F203">
+        <v>10130</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>109</v>
+      </c>
+      <c r="B204" t="s">
+        <v>127</v>
+      </c>
+      <c r="C204" t="s">
+        <v>128</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E204" t="s">
+        <v>129</v>
+      </c>
+      <c r="F204">
+        <v>10151</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>109</v>
+      </c>
+      <c r="B205" t="s">
+        <v>130</v>
+      </c>
+      <c r="C205" t="s">
+        <v>131</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E205" t="s">
+        <v>132</v>
+      </c>
+      <c r="F205">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>109</v>
+      </c>
+      <c r="B206" t="s">
+        <v>133</v>
+      </c>
+      <c r="C206" t="s">
+        <v>134</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E206" t="s">
+        <v>112</v>
+      </c>
+      <c r="F206">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207" t="s">
+        <v>135</v>
+      </c>
+      <c r="C207" t="s">
+        <v>136</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E207" t="s">
+        <v>137</v>
+      </c>
+      <c r="F207">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>109</v>
+      </c>
+      <c r="B208" t="s">
+        <v>138</v>
+      </c>
+      <c r="C208" t="s">
+        <v>139</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E208" t="s">
+        <v>140</v>
+      </c>
+      <c r="F208">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>109</v>
+      </c>
+      <c r="B209" t="s">
+        <v>141</v>
+      </c>
+      <c r="C209" t="s">
+        <v>142</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E209" t="s">
+        <v>34</v>
+      </c>
+      <c r="F209">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>109</v>
+      </c>
+      <c r="B210" t="s">
+        <v>143</v>
+      </c>
+      <c r="C210" t="s">
+        <v>144</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" t="s">
+        <v>10</v>
+      </c>
+      <c r="F210">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>109</v>
+      </c>
+      <c r="B211" t="s">
+        <v>145</v>
+      </c>
+      <c r="C211" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E211" t="s">
+        <v>147</v>
+      </c>
+      <c r="F211">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
